--- a/data/trans_dic/P79$impuestos_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P79$impuestos_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,23</t>
+          <t>1,37; 3,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,72</t>
+          <t>1,92; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,47</t>
+          <t>1,97; 3,46</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,9</t>
+          <t>0,94; 2,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,3</t>
+          <t>0,68; 1,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,41</t>
+          <t>0,9; 1,61</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,33</t>
+          <t>0,11; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,0</t>
+          <t>0,1; 0,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,95</t>
+          <t>0,15; 0,86</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,76</t>
+          <t>1,0; 1,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,53</t>
+          <t>0,93; 1,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,53</t>
+          <t>1,04; 1,6</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>13101</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19391</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31810</t>
+          <t>34411</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7921; 20835</t>
+          <t>7563; 21496</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13262; 26654</t>
+          <t>14997; 30038</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23666; 41956</t>
+          <t>26280; 46033</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>30432</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20711</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45479</t>
+          <t>51143</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16169; 42332</t>
+          <t>20226; 46199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10622; 27292</t>
+          <t>14194; 31022</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31829; 61211</t>
+          <t>38421; 68424</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5860</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>941; 8492</t>
+          <t>766; 8955</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>651; 6481</t>
+          <t>700; 6689</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2404; 12175</t>
+          <t>2149; 12262</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29272; 59052</t>
+          <t>34044; 64435</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29202; 52976</t>
+          <t>33327; 57396</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>67840; 104520</t>
+          <t>72732; 111815</t>
         </is>
       </c>
     </row>
